--- a/GearSage-client/pkgGear/data_raw/abu_spinning_reels_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/abu_spinning_reels_import.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
@@ -45,18 +45,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -71,9 +65,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -404,7 +397,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:S13"/>
   <sheetData>
     <row r="1">
@@ -441,7 +434,7 @@
       <c r="K1" t="str">
         <v>updated_at</v>
       </c>
-      <c r="L1" t="str" s="1">
+      <c r="L1" t="str">
         <v>series_positioning</v>
       </c>
       <c r="M1" t="str">
@@ -459,10 +452,10 @@
       <c r="Q1" t="str">
         <v>market_reference_price</v>
       </c>
-      <c r="R1" t="str" s="1">
+      <c r="R1" t="str">
         <v>player_positioning</v>
       </c>
-      <c r="S1" t="str" s="1">
+      <c r="S1" t="str">
         <v>player_selling_points</v>
       </c>
     </row>
@@ -495,10 +488,10 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Beast%E2%84%A2%20Spinning%20Reel_main.jpg</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="K2" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="L2" t="str">
         <v>重型全水域主力</v>
@@ -554,10 +547,10 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Ike%20Signature%20Spinning%20Reel_main.jpg</v>
       </c>
       <c r="J3" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="K3" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="L3" t="str">
         <v>签名中高端主力</v>
@@ -613,10 +606,10 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Max%E2%84%A2%20Elite%20Spinning%20Reel_main.jpg</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="L4" t="str">
         <v>Max高端入门</v>
@@ -672,10 +665,10 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Max%E2%84%A2%20SX%20Spinning%20Reel_main.jpg</v>
       </c>
       <c r="J5" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="L5" t="str">
         <v>Max中端入门</v>
@@ -731,10 +724,10 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Max%E2%84%A2%20X%20Spinning%20Reel_main.jpg</v>
       </c>
       <c r="J6" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="L6" t="str">
         <v>Max基础入门</v>
@@ -790,10 +783,10 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Max%E2%84%A2%20Pro%20Spinning%20Reel_main.jpg</v>
       </c>
       <c r="J7" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="L7" t="str">
         <v>Max进阶主力</v>
@@ -849,10 +842,10 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Zenon%E2%84%A2%20X%20Spinning%20Reel_main.jpg</v>
       </c>
       <c r="J8" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="K8" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="L8" t="str">
         <v>轻量高端主力</v>
@@ -908,10 +901,10 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Revo%C2%AE%20X%20Spinning%20Reel_main.jpg</v>
       </c>
       <c r="J9" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="K9" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="L9" t="str">
         <v>Revo全能主力</v>
@@ -967,10 +960,10 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Revo%C2%AE%20SX%20Spinning%20Reel_main.jpg</v>
       </c>
       <c r="J10" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="K10" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="L10" t="str">
         <v>Revo中高端主力</v>
@@ -1026,10 +1019,10 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Revo%C2%AE%20Winch%20Spinning%20Reel_main.jpg</v>
       </c>
       <c r="J11" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="K11" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="L11" t="str">
         <v>低速扭矩主力</v>
@@ -1085,10 +1078,10 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Revo%C2%AE%20Rocket%20Spinning%20Reel_main.jpg</v>
       </c>
       <c r="J12" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="K12" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="L12" t="str">
         <v>高速搜索主力</v>
@@ -1144,10 +1137,10 @@
         <v>https://static.gearsage.club/gearsage/Gearimg/images/abu_reels/Max%E2%84%A2%20Pro%20Spinning%20Reel%20(Prior%20Gen)_main.jpg</v>
       </c>
       <c r="J13" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="K13" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="L13" t="str">
         <v>老款Max主力</v>
@@ -1182,7 +1175,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AS46"/>
   <sheetData>
     <row r="1">
@@ -1237,10 +1230,10 @@
       <c r="Q1" t="str">
         <v>bearing_count_roller</v>
       </c>
-      <c r="R1" t="str" s="1">
+      <c r="R1" t="str">
         <v>body_material</v>
       </c>
-      <c r="S1" t="str" s="1">
+      <c r="S1" t="str">
         <v>body_material_tech</v>
       </c>
       <c r="T1" t="str">
@@ -1249,7 +1242,7 @@
       <c r="U1" t="str">
         <v>handle_knob_type</v>
       </c>
-      <c r="V1" t="str" s="1">
+      <c r="V1" t="str">
         <v>official_environment</v>
       </c>
       <c r="W1" t="str">
@@ -1279,16 +1272,16 @@
       <c r="AE1" t="str">
         <v>brake_type_normalized</v>
       </c>
-      <c r="AF1" t="str" s="1">
+      <c r="AF1" t="str">
         <v>fit_style_tags</v>
       </c>
-      <c r="AG1" t="str" s="1">
+      <c r="AG1" t="str">
         <v>min_lure_weight_hint</v>
       </c>
       <c r="AH1" t="str">
         <v>is_compact_body</v>
       </c>
-      <c r="AI1" t="str" s="1">
+      <c r="AI1" t="str">
         <v>handle_style</v>
       </c>
       <c r="AJ1" t="str">
@@ -1297,7 +1290,7 @@
       <c r="AK1" t="str">
         <v>type</v>
       </c>
-      <c r="AL1" t="str" s="1">
+      <c r="AL1" t="str">
         <v>is_sw_edition</v>
       </c>
       <c r="AM1" t="str">
@@ -1306,10 +1299,10 @@
       <c r="AN1" t="str">
         <v>Description</v>
       </c>
-      <c r="AO1" t="str" s="1">
+      <c r="AO1" t="str">
         <v>player_environment</v>
       </c>
-      <c r="AP1" t="str" s="1">
+      <c r="AP1" t="str">
         <v>is_handle_double</v>
       </c>
       <c r="AQ1" t="str">
@@ -1354,7 +1347,7 @@
         <v/>
       </c>
       <c r="K2" t="str">
-        <v>225/6 / 175/8 / 140/10</v>
+        <v>6/225 / 8/175 / 10/140</v>
       </c>
       <c r="L2" t="str">
         <v/>
@@ -1363,7 +1356,7 @@
         <v/>
       </c>
       <c r="N2" t="str">
-        <v>180/10</v>
+        <v>10/180</v>
       </c>
       <c r="O2" t="str">
         <v/>
@@ -1399,10 +1392,10 @@
         <v>36282040007</v>
       </c>
       <c r="Z2" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA2" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB2" t="str">
         <v/>
@@ -1491,7 +1484,7 @@
         <v/>
       </c>
       <c r="K3" t="str">
-        <v>240/8 / 190/10 / 135/12</v>
+        <v>8/240 / 10/190 / 12/135</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -1500,7 +1493,7 @@
         <v/>
       </c>
       <c r="N3" t="str">
-        <v>190/14</v>
+        <v>14/190</v>
       </c>
       <c r="O3" t="str">
         <v/>
@@ -1536,10 +1529,10 @@
         <v>36282040014</v>
       </c>
       <c r="Z3" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA3" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB3" t="str">
         <v/>
@@ -1628,7 +1621,7 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v>210/10 / 180/12 / 150/14</v>
+        <v>10/210 / 12/180 / 14/150</v>
       </c>
       <c r="L4" t="str">
         <v/>
@@ -1637,7 +1630,7 @@
         <v/>
       </c>
       <c r="N4" t="str">
-        <v>210/14</v>
+        <v>14/210</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -1673,10 +1666,10 @@
         <v>36282040021</v>
       </c>
       <c r="Z4" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA4" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB4" t="str">
         <v/>
@@ -1765,7 +1758,7 @@
         <v/>
       </c>
       <c r="K5" t="str">
-        <v>205/12 / 180/14 / 125/20</v>
+        <v>12/205 / 14/180 / 20/125</v>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -1774,7 +1767,7 @@
         <v/>
       </c>
       <c r="N5" t="str">
-        <v>200/20</v>
+        <v>20/200</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -1810,10 +1803,10 @@
         <v>36282040038</v>
       </c>
       <c r="Z5" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA5" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB5" t="str">
         <v/>
@@ -1902,7 +1895,7 @@
         <v/>
       </c>
       <c r="K6" t="str">
-        <v>150/6 / 100/8 / 90/10</v>
+        <v>6/150 / 8/100 / 10/90</v>
       </c>
       <c r="L6" t="str">
         <v/>
@@ -1911,7 +1904,7 @@
         <v/>
       </c>
       <c r="N6" t="str">
-        <v>150/8</v>
+        <v>8/150</v>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -1947,10 +1940,10 @@
         <v>036282010277</v>
       </c>
       <c r="Z6" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA6" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB6" t="str">
         <v/>
@@ -2039,7 +2032,7 @@
         <v/>
       </c>
       <c r="K7" t="str">
-        <v>180/6 / 140/8 / 110/10</v>
+        <v>6/180 / 8/140 / 10/110</v>
       </c>
       <c r="L7" t="str">
         <v/>
@@ -2048,7 +2041,7 @@
         <v/>
       </c>
       <c r="N7" t="str">
-        <v>150/10</v>
+        <v>10/150</v>
       </c>
       <c r="O7" t="str">
         <v/>
@@ -2084,10 +2077,10 @@
         <v>036282010284</v>
       </c>
       <c r="Z7" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA7" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB7" t="str">
         <v/>
@@ -2176,7 +2169,7 @@
         <v/>
       </c>
       <c r="K8" t="str">
-        <v>140/4 / 110/6 / 80/8</v>
+        <v>4/140 / 6/110 / 8/80</v>
       </c>
       <c r="L8" t="str">
         <v/>
@@ -2185,7 +2178,7 @@
         <v/>
       </c>
       <c r="N8" t="str">
-        <v>150/6</v>
+        <v>6/150</v>
       </c>
       <c r="O8" t="str">
         <v/>
@@ -2221,10 +2214,10 @@
         <v>036282737204</v>
       </c>
       <c r="Z8" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA8" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB8" t="str">
         <v/>
@@ -2313,7 +2306,7 @@
         <v/>
       </c>
       <c r="K9" t="str">
-        <v>185/6 / 130/8 / 110/10</v>
+        <v>6/185 / 8/130 / 10/110</v>
       </c>
       <c r="L9" t="str">
         <v/>
@@ -2322,7 +2315,7 @@
         <v/>
       </c>
       <c r="N9" t="str">
-        <v>190/8</v>
+        <v>8/190</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -2358,10 +2351,10 @@
         <v>036282737211</v>
       </c>
       <c r="Z9" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA9" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB9" t="str">
         <v/>
@@ -2450,7 +2443,7 @@
         <v/>
       </c>
       <c r="K10" t="str">
-        <v>225/6 / 175/8 / 140/10</v>
+        <v>6/225 / 8/175 / 10/140</v>
       </c>
       <c r="L10" t="str">
         <v/>
@@ -2459,7 +2452,7 @@
         <v/>
       </c>
       <c r="N10" t="str">
-        <v>180/10</v>
+        <v>10/180</v>
       </c>
       <c r="O10" t="str">
         <v/>
@@ -2495,10 +2488,10 @@
         <v>036282737228</v>
       </c>
       <c r="Z10" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA10" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB10" t="str">
         <v/>
@@ -2587,7 +2580,7 @@
         <v/>
       </c>
       <c r="K11" t="str">
-        <v>210/10 / 180/12 / 150/14</v>
+        <v>10/210 / 12/180 / 14/150</v>
       </c>
       <c r="L11" t="str">
         <v/>
@@ -2596,7 +2589,7 @@
         <v/>
       </c>
       <c r="N11" t="str">
-        <v>210/14</v>
+        <v>14/210</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -2632,10 +2625,10 @@
         <v>036282737235</v>
       </c>
       <c r="Z11" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA11" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB11" t="str">
         <v/>
@@ -2724,7 +2717,7 @@
         <v/>
       </c>
       <c r="K12" t="str">
-        <v>190/2 / 100/4 / 80/6</v>
+        <v>2/190 / 4/100 / 6/80</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -2733,7 +2726,7 @@
         <v/>
       </c>
       <c r="N12" t="str">
-        <v>160/4</v>
+        <v>4/160</v>
       </c>
       <c r="O12" t="str">
         <v/>
@@ -2769,10 +2762,10 @@
         <v>036282737006</v>
       </c>
       <c r="Z12" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA12" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB12" t="str">
         <v/>
@@ -2861,7 +2854,7 @@
         <v/>
       </c>
       <c r="K13" t="str">
-        <v>140/4 / 110/6 / 80/8</v>
+        <v>4/140 / 6/110 / 8/80</v>
       </c>
       <c r="L13" t="str">
         <v/>
@@ -2870,7 +2863,7 @@
         <v/>
       </c>
       <c r="N13" t="str">
-        <v>150/6</v>
+        <v>6/150</v>
       </c>
       <c r="O13" t="str">
         <v/>
@@ -2906,10 +2899,10 @@
         <v>036282737020</v>
       </c>
       <c r="Z13" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA13" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB13" t="str">
         <v/>
@@ -2998,7 +2991,7 @@
         <v/>
       </c>
       <c r="K14" t="str">
-        <v>185/6 / 130/8 / 110/10</v>
+        <v>6/185 / 8/130 / 10/110</v>
       </c>
       <c r="L14" t="str">
         <v/>
@@ -3007,7 +3000,7 @@
         <v/>
       </c>
       <c r="N14" t="str">
-        <v>190/8</v>
+        <v>8/190</v>
       </c>
       <c r="O14" t="str">
         <v/>
@@ -3043,10 +3036,10 @@
         <v>036282737044</v>
       </c>
       <c r="Z14" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA14" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB14" t="str">
         <v/>
@@ -3135,7 +3128,7 @@
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>225/6 / 175/8 / 140/10</v>
+        <v>6/225 / 8/175 / 10/140</v>
       </c>
       <c r="L15" t="str">
         <v/>
@@ -3144,7 +3137,7 @@
         <v/>
       </c>
       <c r="N15" t="str">
-        <v>180/10</v>
+        <v>10/180</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -3180,10 +3173,10 @@
         <v>036282737068</v>
       </c>
       <c r="Z15" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA15" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB15" t="str">
         <v/>
@@ -3272,7 +3265,7 @@
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>210/10 / 180/12 / 150/14</v>
+        <v>10/210 / 12/180 / 14/150</v>
       </c>
       <c r="L16" t="str">
         <v/>
@@ -3281,7 +3274,7 @@
         <v/>
       </c>
       <c r="N16" t="str">
-        <v>210/14</v>
+        <v>14/210</v>
       </c>
       <c r="O16" t="str">
         <v/>
@@ -3317,10 +3310,10 @@
         <v>036282737082</v>
       </c>
       <c r="Z16" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA16" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB16" t="str">
         <v/>
@@ -3409,7 +3402,7 @@
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>190/2 / 100/4 / 80/6</v>
+        <v>2/190 / 4/100 / 6/80</v>
       </c>
       <c r="L17" t="str">
         <v/>
@@ -3418,7 +3411,7 @@
         <v/>
       </c>
       <c r="N17" t="str">
-        <v>160/4</v>
+        <v>4/160</v>
       </c>
       <c r="O17" t="str">
         <v/>
@@ -3454,10 +3447,10 @@
         <v>036282736887</v>
       </c>
       <c r="Z17" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA17" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB17" t="str">
         <v/>
@@ -3546,7 +3539,7 @@
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>140/4 / 110/6 / 80/8</v>
+        <v>4/140 / 6/110 / 8/80</v>
       </c>
       <c r="L18" t="str">
         <v/>
@@ -3555,7 +3548,7 @@
         <v/>
       </c>
       <c r="N18" t="str">
-        <v>150/6</v>
+        <v>6/150</v>
       </c>
       <c r="O18" t="str">
         <v/>
@@ -3591,10 +3584,10 @@
         <v>036282736900</v>
       </c>
       <c r="Z18" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA18" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB18" t="str">
         <v/>
@@ -3683,7 +3676,7 @@
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>185/6 / 130/8 / 110/10</v>
+        <v>6/185 / 8/130 / 10/110</v>
       </c>
       <c r="L19" t="str">
         <v/>
@@ -3692,7 +3685,7 @@
         <v/>
       </c>
       <c r="N19" t="str">
-        <v>190/8</v>
+        <v>8/190</v>
       </c>
       <c r="O19" t="str">
         <v/>
@@ -3728,10 +3721,10 @@
         <v>036282736924</v>
       </c>
       <c r="Z19" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA19" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB19" t="str">
         <v/>
@@ -3820,7 +3813,7 @@
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>225/6 / 175/8 / 140/10</v>
+        <v>6/225 / 8/175 / 10/140</v>
       </c>
       <c r="L20" t="str">
         <v/>
@@ -3829,7 +3822,7 @@
         <v/>
       </c>
       <c r="N20" t="str">
-        <v>180/10</v>
+        <v>10/180</v>
       </c>
       <c r="O20" t="str">
         <v/>
@@ -3865,10 +3858,10 @@
         <v>036282736948</v>
       </c>
       <c r="Z20" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA20" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB20" t="str">
         <v/>
@@ -3957,7 +3950,7 @@
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>210/10 / 180/12 / 150/14</v>
+        <v>10/210 / 12/180 / 14/150</v>
       </c>
       <c r="L21" t="str">
         <v/>
@@ -3966,7 +3959,7 @@
         <v/>
       </c>
       <c r="N21" t="str">
-        <v>210/14</v>
+        <v>14/210</v>
       </c>
       <c r="O21" t="str">
         <v/>
@@ -4002,10 +3995,10 @@
         <v>036282736962</v>
       </c>
       <c r="Z21" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA21" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB21" t="str">
         <v/>
@@ -4094,7 +4087,7 @@
         <v/>
       </c>
       <c r="K22" t="str">
-        <v>250/12 / 205/14 / 150/20</v>
+        <v>12/250 / 14/205 / 20/150</v>
       </c>
       <c r="L22" t="str">
         <v/>
@@ -4103,7 +4096,7 @@
         <v/>
       </c>
       <c r="N22" t="str">
-        <v>200/20</v>
+        <v>20/200</v>
       </c>
       <c r="O22" t="str">
         <v/>
@@ -4139,10 +4132,10 @@
         <v>036282736986</v>
       </c>
       <c r="Z22" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA22" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB22" t="str">
         <v/>
@@ -4231,7 +4224,7 @@
         <v/>
       </c>
       <c r="K23" t="str">
-        <v>190/2 / 100/4 / 80/6</v>
+        <v>2/190 / 4/100 / 6/80</v>
       </c>
       <c r="L23" t="str">
         <v/>
@@ -4240,7 +4233,7 @@
         <v/>
       </c>
       <c r="N23" t="str">
-        <v>160/4</v>
+        <v>4/160</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -4276,10 +4269,10 @@
         <v>036282737105</v>
       </c>
       <c r="Z23" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA23" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB23" t="str">
         <v/>
@@ -4368,7 +4361,7 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>140/4 / 110/6 / 80/8</v>
+        <v>4/140 / 6/110 / 8/80</v>
       </c>
       <c r="L24" t="str">
         <v/>
@@ -4377,7 +4370,7 @@
         <v/>
       </c>
       <c r="N24" t="str">
-        <v>150/6</v>
+        <v>6/150</v>
       </c>
       <c r="O24" t="str">
         <v/>
@@ -4413,10 +4406,10 @@
         <v>036282737129</v>
       </c>
       <c r="Z24" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA24" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB24" t="str">
         <v/>
@@ -4505,7 +4498,7 @@
         <v/>
       </c>
       <c r="K25" t="str">
-        <v>185/6 / 130/8 / 110/10</v>
+        <v>6/185 / 8/130 / 10/110</v>
       </c>
       <c r="L25" t="str">
         <v/>
@@ -4514,7 +4507,7 @@
         <v/>
       </c>
       <c r="N25" t="str">
-        <v>190/8</v>
+        <v>8/190</v>
       </c>
       <c r="O25" t="str">
         <v/>
@@ -4550,10 +4543,10 @@
         <v>036282737143</v>
       </c>
       <c r="Z25" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA25" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB25" t="str">
         <v/>
@@ -4642,7 +4635,7 @@
         <v/>
       </c>
       <c r="K26" t="str">
-        <v>225/6 / 175/8 / 140/10</v>
+        <v>6/225 / 8/175 / 10/140</v>
       </c>
       <c r="L26" t="str">
         <v/>
@@ -4651,7 +4644,7 @@
         <v/>
       </c>
       <c r="N26" t="str">
-        <v>180/10</v>
+        <v>10/180</v>
       </c>
       <c r="O26" t="str">
         <v/>
@@ -4687,10 +4680,10 @@
         <v>036282737167</v>
       </c>
       <c r="Z26" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA26" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB26" t="str">
         <v/>
@@ -4779,7 +4772,7 @@
         <v/>
       </c>
       <c r="K27" t="str">
-        <v>210/10 / 180/12 / 150/14</v>
+        <v>10/210 / 12/180 / 14/150</v>
       </c>
       <c r="L27" t="str">
         <v/>
@@ -4788,7 +4781,7 @@
         <v/>
       </c>
       <c r="N27" t="str">
-        <v>210/14</v>
+        <v>14/210</v>
       </c>
       <c r="O27" t="str">
         <v/>
@@ -4824,10 +4817,10 @@
         <v>036282737181</v>
       </c>
       <c r="Z27" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA27" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB27" t="str">
         <v/>
@@ -4916,7 +4909,7 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>140/4 / 110/6 / 90/10</v>
+        <v>4/140 / 6/110 / 10/90</v>
       </c>
       <c r="L28" t="str">
         <v/>
@@ -4925,7 +4918,7 @@
         <v/>
       </c>
       <c r="N28" t="str">
-        <v>150/6</v>
+        <v>6/150</v>
       </c>
       <c r="O28" t="str">
         <v/>
@@ -4961,10 +4954,10 @@
         <v>036282729780</v>
       </c>
       <c r="Z28" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA28" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB28" t="str">
         <v/>
@@ -5053,7 +5046,7 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>150/6 / 100/8 / 90/10</v>
+        <v>6/150 / 8/100 / 10/90</v>
       </c>
       <c r="L29" t="str">
         <v/>
@@ -5062,7 +5055,7 @@
         <v/>
       </c>
       <c r="N29" t="str">
-        <v>150/8</v>
+        <v>8/150</v>
       </c>
       <c r="O29" t="str">
         <v/>
@@ -5098,10 +5091,10 @@
         <v>036282729797</v>
       </c>
       <c r="Z29" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA29" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB29" t="str">
         <v/>
@@ -5190,7 +5183,7 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>180/6 / 140/8 / 110/10</v>
+        <v>6/180 / 8/140 / 10/110</v>
       </c>
       <c r="L30" t="str">
         <v/>
@@ -5199,7 +5192,7 @@
         <v/>
       </c>
       <c r="N30" t="str">
-        <v>150/10</v>
+        <v>10/150</v>
       </c>
       <c r="O30" t="str">
         <v/>
@@ -5235,10 +5228,10 @@
         <v>036282729803</v>
       </c>
       <c r="Z30" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA30" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB30" t="str">
         <v/>
@@ -5327,7 +5320,7 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>190/8 / 150/10 / 110/12</v>
+        <v>8/190 / 10/150 / 12/110</v>
       </c>
       <c r="L31" t="str">
         <v/>
@@ -5336,7 +5329,7 @@
         <v/>
       </c>
       <c r="N31" t="str">
-        <v>150/14</v>
+        <v>14/150</v>
       </c>
       <c r="O31" t="str">
         <v/>
@@ -5372,10 +5365,10 @@
         <v>036282729810</v>
       </c>
       <c r="Z31" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA31" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB31" t="str">
         <v/>
@@ -5464,7 +5457,7 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>140/4 / 110/6 / 80/8</v>
+        <v>4/140 / 6/110 / 8/80</v>
       </c>
       <c r="L32" t="str">
         <v/>
@@ -5473,7 +5466,7 @@
         <v/>
       </c>
       <c r="N32" t="str">
-        <v>150/6</v>
+        <v>6/150</v>
       </c>
       <c r="O32" t="str">
         <v/>
@@ -5509,10 +5502,10 @@
         <v>036282106376</v>
       </c>
       <c r="Z32" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA32" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB32" t="str">
         <v/>
@@ -5601,7 +5594,7 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>170/6 / 120/8 / 100/10</v>
+        <v>6/170 / 8/120 / 10/100</v>
       </c>
       <c r="L33" t="str">
         <v/>
@@ -5610,7 +5603,7 @@
         <v/>
       </c>
       <c r="N33" t="str">
-        <v>175/8</v>
+        <v>8/175</v>
       </c>
       <c r="O33" t="str">
         <v/>
@@ -5646,10 +5639,10 @@
         <v>036282106383</v>
       </c>
       <c r="Z33" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA33" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB33" t="str">
         <v/>
@@ -5738,7 +5731,7 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v>225/6 / 175/8 / 140/10</v>
+        <v>6/225 / 8/175 / 10/140</v>
       </c>
       <c r="L34" t="str">
         <v/>
@@ -5747,7 +5740,7 @@
         <v/>
       </c>
       <c r="N34" t="str">
-        <v>180/10</v>
+        <v>10/180</v>
       </c>
       <c r="O34" t="str">
         <v/>
@@ -5783,10 +5776,10 @@
         <v>036282106390</v>
       </c>
       <c r="Z34" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA34" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB34" t="str">
         <v/>
@@ -5875,7 +5868,7 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v>240/8 / 190/10 / 135/12</v>
+        <v>8/240 / 10/190 / 12/135</v>
       </c>
       <c r="L35" t="str">
         <v/>
@@ -5884,7 +5877,7 @@
         <v/>
       </c>
       <c r="N35" t="str">
-        <v>190/14</v>
+        <v>14/190</v>
       </c>
       <c r="O35" t="str">
         <v/>
@@ -5920,10 +5913,10 @@
         <v>036282106406</v>
       </c>
       <c r="Z35" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA35" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB35" t="str">
         <v/>
@@ -6012,7 +6005,7 @@
         <v/>
       </c>
       <c r="K36" t="str">
-        <v>140/4 / 110/6 / 80/8</v>
+        <v>4/140 / 6/110 / 8/80</v>
       </c>
       <c r="L36" t="str">
         <v/>
@@ -6021,7 +6014,7 @@
         <v/>
       </c>
       <c r="N36" t="str">
-        <v>150/6</v>
+        <v>6/150</v>
       </c>
       <c r="O36" t="str">
         <v/>
@@ -6057,10 +6050,10 @@
         <v>036282106413</v>
       </c>
       <c r="Z36" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA36" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB36" t="str">
         <v/>
@@ -6149,7 +6142,7 @@
         <v/>
       </c>
       <c r="K37" t="str">
-        <v>170/6 / 120/8 / 100/10</v>
+        <v>6/170 / 8/120 / 10/100</v>
       </c>
       <c r="L37" t="str">
         <v/>
@@ -6158,7 +6151,7 @@
         <v/>
       </c>
       <c r="N37" t="str">
-        <v>175/8</v>
+        <v>8/175</v>
       </c>
       <c r="O37" t="str">
         <v/>
@@ -6194,10 +6187,10 @@
         <v>036282106420</v>
       </c>
       <c r="Z37" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA37" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB37" t="str">
         <v/>
@@ -6286,7 +6279,7 @@
         <v/>
       </c>
       <c r="K38" t="str">
-        <v>225/6 / 175/8 / 140/10</v>
+        <v>6/225 / 8/175 / 10/140</v>
       </c>
       <c r="L38" t="str">
         <v/>
@@ -6295,7 +6288,7 @@
         <v/>
       </c>
       <c r="N38" t="str">
-        <v>180/10</v>
+        <v>10/180</v>
       </c>
       <c r="O38" t="str">
         <v/>
@@ -6331,10 +6324,10 @@
         <v>036282106437</v>
       </c>
       <c r="Z38" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA38" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB38" t="str">
         <v/>
@@ -6423,7 +6416,7 @@
         <v/>
       </c>
       <c r="K39" t="str">
-        <v>240/8 / 190/10 / 135/12</v>
+        <v>8/240 / 10/190 / 12/135</v>
       </c>
       <c r="L39" t="str">
         <v/>
@@ -6432,7 +6425,7 @@
         <v/>
       </c>
       <c r="N39" t="str">
-        <v>190/14</v>
+        <v>14/190</v>
       </c>
       <c r="O39" t="str">
         <v/>
@@ -6468,10 +6461,10 @@
         <v>036282106444</v>
       </c>
       <c r="Z39" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA39" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB39" t="str">
         <v/>
@@ -6560,7 +6553,7 @@
         <v/>
       </c>
       <c r="K40" t="str">
-        <v>225/6 / 175/8 / 140/10</v>
+        <v>6/225 / 8/175 / 10/140</v>
       </c>
       <c r="L40" t="str">
         <v/>
@@ -6569,7 +6562,7 @@
         <v/>
       </c>
       <c r="N40" t="str">
-        <v>180/10</v>
+        <v>10/180</v>
       </c>
       <c r="O40" t="str">
         <v/>
@@ -6605,10 +6598,10 @@
         <v>036282106451</v>
       </c>
       <c r="Z40" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA40" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB40" t="str">
         <v/>
@@ -6697,7 +6690,7 @@
         <v/>
       </c>
       <c r="K41" t="str">
-        <v>170/6 / 120/8 / 100/10</v>
+        <v>6/170 / 8/120 / 10/100</v>
       </c>
       <c r="L41" t="str">
         <v/>
@@ -6706,7 +6699,7 @@
         <v/>
       </c>
       <c r="N41" t="str">
-        <v>175/8</v>
+        <v>8/175</v>
       </c>
       <c r="O41" t="str">
         <v/>
@@ -6742,10 +6735,10 @@
         <v>036282106468</v>
       </c>
       <c r="Z41" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA41" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB41" t="str">
         <v/>
@@ -6834,7 +6827,7 @@
         <v/>
       </c>
       <c r="K42" t="str">
-        <v>225/6 / 175/8 / 140/10</v>
+        <v>6/225 / 8/175 / 10/140</v>
       </c>
       <c r="L42" t="str">
         <v/>
@@ -6843,7 +6836,7 @@
         <v/>
       </c>
       <c r="N42" t="str">
-        <v>180/10</v>
+        <v>10/180</v>
       </c>
       <c r="O42" t="str">
         <v/>
@@ -6879,10 +6872,10 @@
         <v>036282106475</v>
       </c>
       <c r="Z42" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA42" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB42" t="str">
         <v/>
@@ -6971,7 +6964,7 @@
         <v/>
       </c>
       <c r="K43" t="str">
-        <v>240/8 / 190/10 / 135/12</v>
+        <v>8/240 / 10/190 / 12/135</v>
       </c>
       <c r="L43" t="str">
         <v/>
@@ -6980,7 +6973,7 @@
         <v/>
       </c>
       <c r="N43" t="str">
-        <v>190/14</v>
+        <v>14/190</v>
       </c>
       <c r="O43" t="str">
         <v/>
@@ -7016,10 +7009,10 @@
         <v>036282106482</v>
       </c>
       <c r="Z43" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA43" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB43" t="str">
         <v/>
@@ -7108,7 +7101,7 @@
         <v/>
       </c>
       <c r="K44" t="str">
-        <v>190/2 / 100/4 / 80/6</v>
+        <v>2/190 / 4/100 / 6/80</v>
       </c>
       <c r="L44" t="str">
         <v/>
@@ -7117,7 +7110,7 @@
         <v/>
       </c>
       <c r="N44" t="str">
-        <v>160/4</v>
+        <v>4/160</v>
       </c>
       <c r="O44" t="str">
         <v/>
@@ -7153,10 +7146,10 @@
         <v>036282984110</v>
       </c>
       <c r="Z44" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA44" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB44" t="str">
         <v/>
@@ -7245,7 +7238,7 @@
         <v/>
       </c>
       <c r="K45" t="str">
-        <v>140/4 / 110/6 / 80/8</v>
+        <v>4/140 / 6/110 / 8/80</v>
       </c>
       <c r="L45" t="str">
         <v/>
@@ -7254,7 +7247,7 @@
         <v/>
       </c>
       <c r="N45" t="str">
-        <v>150/6</v>
+        <v>6/150</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -7290,10 +7283,10 @@
         <v>036282984172</v>
       </c>
       <c r="Z45" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA45" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB45" t="str">
         <v/>
@@ -7382,7 +7375,7 @@
         <v/>
       </c>
       <c r="K46" t="str">
-        <v>185/6 / 130/8 / 110/10</v>
+        <v>6/185 / 8/130 / 10/110</v>
       </c>
       <c r="L46" t="str">
         <v/>
@@ -7391,7 +7384,7 @@
         <v/>
       </c>
       <c r="N46" t="str">
-        <v>190/8</v>
+        <v>8/190</v>
       </c>
       <c r="O46" t="str">
         <v/>
@@ -7427,10 +7420,10 @@
         <v>036282984295</v>
       </c>
       <c r="Z46" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AA46" t="str">
-        <v>2026-04-21T13:40:16.586Z</v>
+        <v>2026-04-21T17:00:30.007Z</v>
       </c>
       <c r="AB46" t="str">
         <v/>
